--- a/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Дата подписания (принятия) работ (услуг)</t>
   </si>
   <si>
-    <t xml:space="preserve">{organization.organization}, {organization.address}</t>
+    <t xml:space="preserve">{organization.organization}, город {organization.city}, {organization.index}, {organization.address}</t>
   </si>
   <si>
     <t>{organization.bin}</t>

--- a/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
@@ -189,16 +189,16 @@
     <t>{nights}</t>
   </si>
   <si>
-    <t>{organization.costPerDay}</t>
-  </si>
-  <si>
-    <t>{totalPrice}</t>
+    <t>{costPerDayFormatted}</t>
+  </si>
+  <si>
+    <t>{totalCost}</t>
   </si>
   <si>
     <t>х</t>
   </si>
   <si>
-    <t xml:space="preserve">{totalPriceWords} тенге 00 тиын</t>
+    <t xml:space="preserve">{totalCostRu} тенге 00 тиын</t>
   </si>
   <si>
     <t>ИП</t>

--- a/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
@@ -162,10 +162,10 @@
     <t xml:space="preserve">Дата подписания (принятия) работ (услуг)</t>
   </si>
   <si>
-    <t xml:space="preserve">{organization.organization}, город {organization.city}, {organization.index}, {organization.address}</t>
-  </si>
-  <si>
-    <t>{organization.bin}</t>
+    <t xml:space="preserve">{customer.organization.organization}, город {customer.organization.city}, {customer.organization.index}, {customer.organization.address}</t>
+  </si>
+  <si>
+    <t>{customer.organization.bin}</t>
   </si>
   <si>
     <t xml:space="preserve">Индивидуальный предприниматель «NomadDocs»  Жалтырбаев Әділет Ғалымұлы                                                                               Карагандинская область, г. Караганда,район имени Казыбек Би, улица Гапеева, дом 15/1, блок Б, квартира №101</t>

--- a/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Дата подписания (принятия) работ (услуг)</t>
   </si>
   <si>
-    <t xml:space="preserve">{customer.organization.organization}, город {customer.organization.city}, {customer.organization.index}, {customer.organization.address}</t>
+    <t xml:space="preserve">{customer.organization.organization}, город {customer.organization.city}, {customer.organization.index} {customer.organization.address}</t>
   </si>
   <si>
     <t>{customer.organization.bin}</t>

--- a/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Completed Work Certificates.xlsx
@@ -198,7 +198,7 @@
     <t>х</t>
   </si>
   <si>
-    <t xml:space="preserve">{totalCostRu} тенге 00 тиын</t>
+    <t xml:space="preserve">{totalCostRu} тенге{totalCostCentsRu} тиын</t>
   </si>
   <si>
     <t>ИП</t>
